--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_quality_issue_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_quality_issue_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t>项目编号</t>
   </si>
@@ -433,94 +433,115 @@
     <t>PJ-2025-008</t>
   </si>
   <si>
+    <t>2025-13-20</t>
+  </si>
+  <si>
+    <t>赵敏</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>李雪</t>
+  </si>
+  <si>
+    <t>20205/03/05</t>
+  </si>
+  <si>
+    <t>20205/04/15</t>
+  </si>
+  <si>
+    <t>钱海</t>
+  </si>
+  <si>
+    <t>20250/03/18</t>
+  </si>
+  <si>
+    <t>2025-13-01</t>
+  </si>
+  <si>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>王鹏</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>20250/03/25</t>
+  </si>
+  <si>
+    <t>2025-3-25</t>
+  </si>
+  <si>
     <t>秦川</t>
   </si>
   <si>
+    <t>20250/04/01</t>
+  </si>
+  <si>
+    <t>黄磊</t>
+  </si>
+  <si>
     <t>PJ-2025-005</t>
   </si>
   <si>
-    <t>PJ-2025-004</t>
-  </si>
-  <si>
-    <t>20250/03/05</t>
-  </si>
-  <si>
-    <t>2025/04/01</t>
-  </si>
-  <si>
-    <t>钱海</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>王鹏</t>
-  </si>
-  <si>
-    <t>PJ-2025-006</t>
+    <t>2025年5月10日</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>20205/03/28</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025/03/10</t>
   </si>
   <si>
     <t>待定</t>
   </si>
   <si>
-    <t>赵敏</t>
-  </si>
-  <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>2025.3.15</t>
-  </si>
-  <si>
-    <t>2025.4.20</t>
-  </si>
-  <si>
-    <t>2025年03月28日</t>
-  </si>
-  <si>
-    <t>20205/04/10</t>
-  </si>
-  <si>
-    <t>郭伟</t>
+    <t>2025.5.10</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>2025年04月10日</t>
   </si>
   <si>
     <t>2025-13-25</t>
   </si>
   <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>李雪</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>2025-04-32</t>
-  </si>
-  <si>
-    <t>2025/5/10</t>
-  </si>
-  <si>
-    <t>2025/4/12</t>
+    <t>2025年04月01日</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>2025年4月20日</t>
   </si>
   <si>
     <t>2025-03</t>
   </si>
   <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>2025年2月10日</t>
-  </si>
-  <si>
-    <t>2025.5.10</t>
-  </si>
-  <si>
-    <t>2025-04</t>
+    <t>20250/03/20</t>
+  </si>
+  <si>
+    <t>2025年3月15日</t>
+  </si>
+  <si>
+    <t>2025/3/5</t>
+  </si>
+  <si>
+    <t>2025-4-25</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1284,7 @@
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="H12" t="s">
         <v>28</v>
@@ -1305,12 +1326,12 @@
         <v>39</v>
       </c>
       <c r="U12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
@@ -1370,7 +1391,7 @@
         <v>39</v>
       </c>
       <c r="U13" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
@@ -1393,7 +1414,7 @@
         <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H14" t="s">
         <v>63</v>
@@ -1440,7 +1461,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1458,7 +1479,7 @@
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
         <v>75</v>
@@ -1491,7 +1512,7 @@
         <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="S15" t="s">
         <v>81</v>
@@ -1500,12 +1521,12 @@
         <v>39</v>
       </c>
       <c r="U15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1523,7 +1544,7 @@
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
@@ -1550,7 +1571,7 @@
         <v>88</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q16" t="s">
         <v>75</v>
@@ -1565,12 +1586,12 @@
         <v>89</v>
       </c>
       <c r="U16" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
@@ -1630,12 +1651,12 @@
         <v>89</v>
       </c>
       <c r="U17" t="s">
-        <v>148</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
@@ -1695,12 +1716,12 @@
         <v>89</v>
       </c>
       <c r="U18" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s">
         <v>110</v>
@@ -1760,12 +1781,12 @@
         <v>39</v>
       </c>
       <c r="U19" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
         <v>121</v>
@@ -1816,7 +1837,7 @@
         <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="S20" t="s">
         <v>131</v>
@@ -1825,12 +1846,12 @@
         <v>89</v>
       </c>
       <c r="U20" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
         <v>110</v>
@@ -1875,7 +1896,7 @@
         <v>138</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="Q21" t="s">
         <v>63</v>
@@ -1890,12 +1911,12 @@
         <v>89</v>
       </c>
       <c r="U21" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
@@ -1955,12 +1976,12 @@
         <v>39</v>
       </c>
       <c r="U22" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -2020,12 +2041,12 @@
         <v>39</v>
       </c>
       <c r="U23" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
@@ -2070,13 +2091,13 @@
         <v>69</v>
       </c>
       <c r="P24" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="Q24" t="s">
         <v>71</v>
       </c>
       <c r="R24" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="S24" t="s">
         <v>71</v>
@@ -2085,12 +2106,12 @@
         <v>39</v>
       </c>
       <c r="U24" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -2150,7 +2171,7 @@
         <v>39</v>
       </c>
       <c r="U25" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
@@ -2200,7 +2221,7 @@
         <v>88</v>
       </c>
       <c r="P26" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="Q26" t="s">
         <v>75</v>
@@ -2215,12 +2236,12 @@
         <v>89</v>
       </c>
       <c r="U26" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -2238,7 +2259,7 @@
         <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
         <v>93</v>
@@ -2280,12 +2301,12 @@
         <v>89</v>
       </c>
       <c r="U27" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
@@ -2345,12 +2366,12 @@
         <v>89</v>
       </c>
       <c r="U28" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
         <v>110</v>
@@ -2368,7 +2389,7 @@
         <v>114</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="H29" t="s">
         <v>71</v>
@@ -2410,12 +2431,12 @@
         <v>39</v>
       </c>
       <c r="U29" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
         <v>121</v>
@@ -2433,7 +2454,7 @@
         <v>125</v>
       </c>
       <c r="G30" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="H30" t="s">
         <v>38</v>
@@ -2475,12 +2496,12 @@
         <v>89</v>
       </c>
       <c r="U30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
@@ -2525,7 +2546,7 @@
         <v>138</v>
       </c>
       <c r="P31" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="Q31" t="s">
         <v>63</v>
@@ -2540,12 +2561,12 @@
         <v>89</v>
       </c>
       <c r="U31" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
@@ -2605,12 +2626,12 @@
         <v>39</v>
       </c>
       <c r="U32" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -2655,13 +2676,13 @@
         <v>53</v>
       </c>
       <c r="P33" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="Q33" t="s">
         <v>55</v>
       </c>
       <c r="R33" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="S33" t="s">
         <v>55</v>
@@ -2670,12 +2691,12 @@
         <v>39</v>
       </c>
       <c r="U33" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
         <v>57</v>
@@ -2726,7 +2747,7 @@
         <v>71</v>
       </c>
       <c r="R34" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="S34" t="s">
         <v>71</v>
@@ -2735,12 +2756,12 @@
         <v>39</v>
       </c>
       <c r="U34" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
@@ -2805,7 +2826,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -2856,7 +2877,7 @@
         <v>75</v>
       </c>
       <c r="R36" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="S36" t="s">
         <v>75</v>
@@ -2865,12 +2886,12 @@
         <v>89</v>
       </c>
       <c r="U36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
@@ -2888,7 +2909,7 @@
         <v>45</v>
       </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="H37" t="s">
         <v>93</v>
@@ -2930,12 +2951,12 @@
         <v>89</v>
       </c>
       <c r="U37" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
@@ -2986,7 +3007,7 @@
         <v>81</v>
       </c>
       <c r="R38" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="S38" t="s">
         <v>81</v>
@@ -2995,7 +3016,7 @@
         <v>89</v>
       </c>
       <c r="U38" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39">
@@ -3018,7 +3039,7 @@
         <v>114</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="H39" t="s">
         <v>71</v>
@@ -3051,7 +3072,7 @@
         <v>36</v>
       </c>
       <c r="R39" t="s">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="S39" t="s">
         <v>38</v>
@@ -3060,12 +3081,12 @@
         <v>39</v>
       </c>
       <c r="U39" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="B40" t="s">
         <v>121</v>
@@ -3125,12 +3146,12 @@
         <v>89</v>
       </c>
       <c r="U40" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
         <v>110</v>
@@ -3190,12 +3211,12 @@
         <v>89</v>
       </c>
       <c r="U41" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
@@ -3246,7 +3267,7 @@
         <v>36</v>
       </c>
       <c r="R42" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="S42" t="s">
         <v>38</v>
@@ -3255,12 +3276,12 @@
         <v>39</v>
       </c>
       <c r="U42" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
         <v>41</v>
@@ -3320,12 +3341,12 @@
         <v>39</v>
       </c>
       <c r="U43" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -3376,7 +3397,7 @@
         <v>71</v>
       </c>
       <c r="R44" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="S44" t="s">
         <v>71</v>
@@ -3385,12 +3406,12 @@
         <v>39</v>
       </c>
       <c r="U44" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -3408,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s">
         <v>75</v>
@@ -3450,12 +3471,12 @@
         <v>39</v>
       </c>
       <c r="U45" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
         <v>22</v>
@@ -3506,7 +3527,7 @@
         <v>75</v>
       </c>
       <c r="R46" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="S46" t="s">
         <v>75</v>
@@ -3515,7 +3536,7 @@
         <v>89</v>
       </c>
       <c r="U46" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -3538,7 +3559,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="s">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
         <v>93</v>
@@ -3580,12 +3601,12 @@
         <v>89</v>
       </c>
       <c r="U47" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -3645,12 +3666,12 @@
         <v>89</v>
       </c>
       <c r="U48" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
         <v>110</v>
@@ -3710,12 +3731,12 @@
         <v>39</v>
       </c>
       <c r="U49" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B50" t="s">
         <v>121</v>
@@ -3766,7 +3787,7 @@
         <v>36</v>
       </c>
       <c r="R50" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="S50" t="s">
         <v>131</v>
@@ -3775,12 +3796,12 @@
         <v>89</v>
       </c>
       <c r="U50" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="B51" t="s">
         <v>110</v>
@@ -3845,7 +3866,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
@@ -3896,7 +3917,7 @@
         <v>36</v>
       </c>
       <c r="R52" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="S52" t="s">
         <v>38</v>
@@ -3905,12 +3926,12 @@
         <v>39</v>
       </c>
       <c r="U52" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
         <v>41</v>
@@ -3970,12 +3991,12 @@
         <v>39</v>
       </c>
       <c r="U53" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -3993,7 +4014,7 @@
         <v>61</v>
       </c>
       <c r="G54" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="H54" t="s">
         <v>63</v>
@@ -4035,7 +4056,7 @@
         <v>39</v>
       </c>
       <c r="U54" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55">
@@ -4100,12 +4121,12 @@
         <v>39</v>
       </c>
       <c r="U55" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
@@ -4150,7 +4171,7 @@
         <v>88</v>
       </c>
       <c r="P56" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="Q56" t="s">
         <v>75</v>
@@ -4170,7 +4191,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>41</v>
@@ -4188,7 +4209,7 @@
         <v>45</v>
       </c>
       <c r="G57" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s">
         <v>93</v>
@@ -4230,12 +4251,12 @@
         <v>89</v>
       </c>
       <c r="U57" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>57</v>
@@ -4280,7 +4301,7 @@
         <v>107</v>
       </c>
       <c r="P58" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="Q58" t="s">
         <v>81</v>
@@ -4295,12 +4316,12 @@
         <v>89</v>
       </c>
       <c r="U58" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>110</v>
@@ -4360,12 +4381,12 @@
         <v>39</v>
       </c>
       <c r="U59" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
         <v>121</v>
@@ -4383,7 +4404,7 @@
         <v>125</v>
       </c>
       <c r="G60" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="H60" t="s">
         <v>38</v>
@@ -4425,12 +4446,12 @@
         <v>89</v>
       </c>
       <c r="U60" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s">
         <v>110</v>
@@ -4490,12 +4511,12 @@
         <v>89</v>
       </c>
       <c r="U61" t="s">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -4555,12 +4576,12 @@
         <v>39</v>
       </c>
       <c r="U62" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>41</v>
@@ -4605,7 +4626,7 @@
         <v>53</v>
       </c>
       <c r="P63" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="Q63" t="s">
         <v>55</v>
@@ -4620,12 +4641,12 @@
         <v>39</v>
       </c>
       <c r="U63" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B64" t="s">
         <v>57</v>
@@ -4685,12 +4706,12 @@
         <v>39</v>
       </c>
       <c r="U64" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
         <v>22</v>
@@ -4750,12 +4771,12 @@
         <v>39</v>
       </c>
       <c r="U65" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -4800,13 +4821,13 @@
         <v>88</v>
       </c>
       <c r="P66" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="Q66" t="s">
         <v>75</v>
       </c>
       <c r="R66" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="S66" t="s">
         <v>75</v>
@@ -4815,12 +4836,12 @@
         <v>89</v>
       </c>
       <c r="U66" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
         <v>41</v>
@@ -4880,12 +4901,12 @@
         <v>89</v>
       </c>
       <c r="U67" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s">
         <v>57</v>
@@ -4936,7 +4957,7 @@
         <v>81</v>
       </c>
       <c r="R68" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="S68" t="s">
         <v>81</v>
@@ -4945,12 +4966,12 @@
         <v>89</v>
       </c>
       <c r="U68" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="B69" t="s">
         <v>110</v>
@@ -4968,7 +4989,7 @@
         <v>114</v>
       </c>
       <c r="G69" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="H69" t="s">
         <v>71</v>
@@ -5010,12 +5031,12 @@
         <v>39</v>
       </c>
       <c r="U69" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
@@ -5075,12 +5096,12 @@
         <v>89</v>
       </c>
       <c r="U70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
         <v>110</v>
@@ -5125,7 +5146,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="Q71" t="s">
         <v>63</v>
@@ -5140,12 +5161,12 @@
         <v>89</v>
       </c>
       <c r="U71" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
@@ -5163,7 +5184,7 @@
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="H72" t="s">
         <v>28</v>
@@ -5205,12 +5226,12 @@
         <v>39</v>
       </c>
       <c r="U72" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
         <v>41</v>
@@ -5228,7 +5249,7 @@
         <v>45</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="H73" t="s">
         <v>47</v>
@@ -5261,7 +5282,7 @@
         <v>55</v>
       </c>
       <c r="R73" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="S73" t="s">
         <v>55</v>
@@ -5270,12 +5291,12 @@
         <v>39</v>
       </c>
       <c r="U73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
         <v>57</v>
@@ -5293,7 +5314,7 @@
         <v>61</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
       <c r="H74" t="s">
         <v>63</v>
@@ -5326,7 +5347,7 @@
         <v>71</v>
       </c>
       <c r="R74" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="S74" t="s">
         <v>71</v>
@@ -5335,12 +5356,12 @@
         <v>39</v>
       </c>
       <c r="U74" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -5400,12 +5421,12 @@
         <v>39</v>
       </c>
       <c r="U75" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5465,12 +5486,12 @@
         <v>89</v>
       </c>
       <c r="U76" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
         <v>41</v>
@@ -5488,7 +5509,7 @@
         <v>45</v>
       </c>
       <c r="G77" t="s">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="H77" t="s">
         <v>93</v>
@@ -5530,12 +5551,12 @@
         <v>89</v>
       </c>
       <c r="U77" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B78" t="s">
         <v>57</v>
@@ -5553,7 +5574,7 @@
         <v>61</v>
       </c>
       <c r="G78" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="H78" t="s">
         <v>75</v>
@@ -5595,12 +5616,12 @@
         <v>89</v>
       </c>
       <c r="U78" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B79" t="s">
         <v>110</v>
@@ -5660,12 +5681,12 @@
         <v>39</v>
       </c>
       <c r="U79" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B80" t="s">
         <v>121</v>
@@ -5716,7 +5737,7 @@
         <v>36</v>
       </c>
       <c r="R80" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="S80" t="s">
         <v>131</v>
@@ -5730,7 +5751,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
         <v>110</v>
@@ -5790,7 +5811,7 @@
         <v>89</v>
       </c>
       <c r="U81" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
